--- a/data/japan_stock_dividend_db_out.xlsx
+++ b/data/japan_stock_dividend_db_out.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
           <t>YahooURL</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>BuffettCodeURL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IRBANKURL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -483,6 +493,16 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>https://finance.yahoo.co.jp/quote/9733.T</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.buffett-code.com/company/9733/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://irbank.net/E04824/results</t>
         </is>
       </c>
     </row>
